--- a/education_forms/047_parent_teacher_conference_form--education_forms.xlsx
+++ b/education_forms/047_parent_teacher_conference_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>meeting_time</t>
+          <t>meeting_time_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Meeting Time</t>
+          <t>Meeting Time 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>subject_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Subject 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>meeting_location</t>
+          <t>meeting_location_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Meeting Location</t>
+          <t>Meeting Location 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,63 +1165,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>subject_choices</t>
+          <t>subject_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>subject_choices</t>
+          <t>subject_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meeting_status_choices</t>
+          <t>subject_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,10 +1233,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>meeting_status_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>inactive</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
